--- a/data/trans_orig/P79A2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P79A2_2023-Clase-trans_orig.xlsx
@@ -725,27 +725,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>9658</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8219</t>
+          <t>10867</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9811</t>
+          <t>11480</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8589</t>
+          <t>7356</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10273</t>
+          <t>13411</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>5562</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>587</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>6642</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>47,45%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8219</t>
+          <t>10867</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8219</t>
+          <t>10867</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8219</t>
+          <t>10867</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>10296</t>
+          <t>13998</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10296</t>
+          <t>13998</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10296</t>
+          <t>13998</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,27 +1068,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>2373</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>6921</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>9956</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6497</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>11074</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>4530</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,34%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>6921</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>6921</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>6921</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>11074</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>11074</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>11074</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,27 +1411,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>7239</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1446,27 +1446,27 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>458</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4773</t>
+          <t>6832</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1708</t>
+          <t>3885</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>91,96%</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>5517</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>736</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>796</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>60,78%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>7239</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>7239</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>7239</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>6037</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6037</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6037</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12405</t>
+          <t>18051</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>11822</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16424</t>
+          <t>22238</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>13381</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5467</t>
+          <t>9478</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10406</t>
+          <t>15496</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>20749</t>
+          <t>31432</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15333</t>
+          <t>24874</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25052</t>
+          <t>36081</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>87,49%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>6908</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>2721</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10749</t>
+          <t>13137</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>787</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>9810</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14293</t>
+          <t>16368</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>39,69%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18495</t>
+          <t>24959</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18495</t>
+          <t>24959</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18495</t>
+          <t>24959</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11131</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11131</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11131</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>29626</t>
+          <t>41242</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>29626</t>
+          <t>41242</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>29626</t>
+          <t>41242</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6260</t>
+          <t>8197</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7720</t>
+          <t>10977</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>15823</t>
+          <t>20950</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8638</t>
+          <t>13065</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19680</t>
+          <t>25596</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>22083</t>
+          <t>29146</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>20462</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26518</t>
+          <t>34386</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>81,08%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>944</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>7663</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7960</t>
+          <t>9542</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15145</t>
+          <t>17427</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>9743</t>
+          <t>13266</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16820</t>
+          <t>21950</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>51,75%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23783</t>
+          <t>30492</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23783</t>
+          <t>30492</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23783</t>
+          <t>30492</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>31826</t>
+          <t>42412</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>31826</t>
+          <t>42412</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>31826</t>
+          <t>42412</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10482</t>
+          <t>15250</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3940</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16505</t>
+          <t>20408</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>10644</t>
+          <t>17072</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>10544</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16871</t>
+          <t>22340</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>85,74%</t>
         </is>
       </c>
     </row>
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>10371</t>
+          <t>8982</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16913</t>
+          <t>15914</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>10371</t>
+          <t>8982</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4144</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16910</t>
+          <t>15510</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>59,53%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20853</t>
+          <t>24232</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20853</t>
+          <t>24232</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20853</t>
+          <t>24232</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>21015</t>
+          <t>26054</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>21015</t>
+          <t>26054</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>21015</t>
+          <t>26054</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>35732</t>
+          <t>48431</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29128</t>
+          <t>39920</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40477</t>
+          <t>54614</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>41521</t>
+          <t>57487</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30690</t>
+          <t>46037</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49709</t>
+          <t>64488</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>77254</t>
+          <t>105919</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64371</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87131</t>
+          <t>116699</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>80,66%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>10157</t>
+          <t>15298</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5412</t>
+          <t>9115</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16761</t>
+          <t>23809</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>21602</t>
+          <t>23471</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13414</t>
+          <t>16470</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>32433</t>
+          <t>34921</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>31758</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>21881</t>
+          <t>27989</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>44641</t>
+          <t>52004</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>35,94%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>45889</t>
+          <t>63729</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>45889</t>
+          <t>63729</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45889</t>
+          <t>63729</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>63123</t>
+          <t>80958</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>63123</t>
+          <t>80958</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>63123</t>
+          <t>80958</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>109012</t>
+          <t>144688</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>109012</t>
+          <t>144688</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>109012</t>
+          <t>144688</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
